--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487977_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487977_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1294</v>
+        <v>4.6285</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8682</v>
+        <v>6.4234</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7388</v>
+        <v>-1.795</v>
       </c>
       <c r="G2" t="n">
         <v>-1.08</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6122</v>
+        <v>-1.1132</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.8095</v>
+        <v>-1.2543</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1973</v>
+        <v>0.1412</v>
       </c>
       <c r="V2" t="n">
         <v>5.2358</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9746</v>
+        <v>4.1783</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1906</v>
+        <v>2.3943</v>
       </c>
       <c r="F3" t="n">
         <v>1.784</v>
@@ -688,10 +688,10 @@
         <v>0.3964</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4478</v>
+        <v>0.6516</v>
       </c>
       <c r="T3" t="n">
-        <v>0.011</v>
+        <v>0.2148</v>
       </c>
       <c r="U3" t="n">
         <v>0.4368</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2144</v>
+        <v>1.8422</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9131</v>
+        <v>0.7093</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3014</v>
+        <v>1.1329</v>
       </c>
       <c r="G5" t="n">
         <v>0.5538</v>
@@ -844,13 +844,13 @@
         <v>0.7929</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8678</v>
+        <v>0.4956</v>
       </c>
       <c r="T5" t="n">
-        <v>0.503</v>
+        <v>0.2992</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3648</v>
+        <v>0.1963</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3105</v>
+        <v>0.5424</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0422</v>
+        <v>0.1615</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3528</v>
+        <v>0.3808</v>
       </c>
       <c r="G6" t="n">
         <v>0.156</v>
@@ -922,13 +922,13 @@
         <v>0.1982</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0437</v>
+        <v>0.1881</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0624</v>
+        <v>0.1413</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2048</v>
+        <v>0.185</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6518</v>
+        <v>-0.3462</v>
       </c>
       <c r="F7" t="n">
-        <v>0.447</v>
+        <v>0.5313</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4643</v>
@@ -1000,13 +1000,13 @@
         <v>0.7929</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2669</v>
+        <v>0.123</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1138</v>
+        <v>0.1918</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1531</v>
+        <v>-0.0689</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2666</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8267</v>
+        <v>-1.9628</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0668</v>
+        <v>0.8466</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8936</v>
+        <v>-2.8093</v>
       </c>
       <c r="G8" t="n">
         <v>-2.6906</v>
@@ -1078,13 +1078,13 @@
         <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2692</v>
+        <v>0.1332</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3889</v>
+        <v>-0.6091</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6581</v>
+        <v>0.7423</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8978</v>
+        <v>-2.2844</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1085</v>
+        <v>1.4973</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.0063</v>
+        <v>-3.7816</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6945</v>
@@ -1156,13 +1156,13 @@
         <v>0.5947</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7372</v>
+        <v>0.3506</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7967</v>
+        <v>0.1855</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0595</v>
+        <v>0.1651</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5441</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. GEA BECERRA</t>
+          <t>A. VAZQUEZ ASTILLEROS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.952</v>
+        <v>-2.7311</v>
       </c>
       <c r="E10" t="n">
-        <v>0.498</v>
+        <v>-2.0168</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.45</v>
+        <v>-0.7143</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.7332</v>
+        <v>-2.7481</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7499</v>
+        <v>0.378</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.9833</v>
+        <v>-3.1261</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0167</v>
+        <v>-1.0244</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3348</v>
+        <v>0.3701</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3181</v>
+        <v>-1.3945</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.75</v>
+        <v>-1.7237</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.0848</v>
+        <v>0.0078</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.6652</v>
+        <v>-1.7315</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9822</v>
+        <v>0.7929</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3787</v>
+        <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4675</v>
+        <v>-0.1019</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3889</v>
+        <v>-0.3184</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.2165</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2666</v>
+        <v>-0.674</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2666</v>
+        <v>-0.674</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ ASTILLEROS</t>
+          <t>M. PEREZ SARRABLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0616</v>
+        <v>-2.8471</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.572</v>
+        <v>0.3558</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4897</v>
+        <v>-3.203</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7481</v>
+        <v>-1.9706</v>
       </c>
       <c r="H11" t="n">
-        <v>0.378</v>
+        <v>0.8647</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.1261</v>
+        <v>-2.8352</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0244</v>
+        <v>2.8988</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3701</v>
+        <v>2.4011</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3945</v>
+        <v>0.4977</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7237</v>
+        <v>-4.8694</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0078</v>
+        <v>-1.5365</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7315</v>
+        <v>-3.3329</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7929</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.3609</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4324</v>
+        <v>-0.1082</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8736</v>
+        <v>-0.1889</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4411</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.674</v>
+        <v>2.0068</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.674</v>
+        <v>2.0068</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. FERNANDEZ CAMPOS</t>
+          <t>E. GEA BECERRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4321</v>
+        <v>-3.5902</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5872</v>
+        <v>-0.0279</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8449</v>
+        <v>-3.5623</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.4637</v>
+        <v>-4.7332</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6713</v>
+        <v>-0.7499</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.135</v>
+        <v>-3.9833</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4862</v>
+        <v>1.0167</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9893</v>
+        <v>2.3348</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.4755</v>
+        <v>-1.3181</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9775</v>
+        <v>-5.75</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.318</v>
+        <v>-3.0848</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.6595</v>
+        <v>-2.6652</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1982</v>
+        <v>1.9822</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1893</v>
+        <v>-0.3964</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3876</v>
+        <v>2.3787</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2407</v>
+        <v>-1.1057</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4957</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.745</v>
+        <v>-0.191</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4074</v>
+        <v>0.2666</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.4074</v>
+        <v>0.2666</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. PEREZ SARRABLO</t>
+          <t>H. FERNANDEZ CAMPOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7454</v>
+        <v>-3.9561</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3178</v>
+        <v>-2.8304</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.4276</v>
+        <v>-1.1257</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.9706</v>
+        <v>-4.4637</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8647</v>
+        <v>0.6713</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.8352</v>
+        <v>-5.135</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8988</v>
+        <v>-1.4862</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4011</v>
+        <v>0.9893</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4977</v>
+        <v>-2.4755</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.8694</v>
+        <v>-2.9775</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5365</v>
+        <v>-0.318</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.3329</v>
+        <v>-2.6595</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.7751</v>
+        <v>0.1982</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.3609</v>
+        <v>-1.1893</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0065</v>
+        <v>0.7167</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8625</v>
+        <v>0.2525</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.144</v>
+        <v>0.4642</v>
       </c>
       <c r="V13" t="n">
-        <v>2.0068</v>
+        <v>-0.4074</v>
       </c>
       <c r="W13" t="n">
-        <v>2.0068</v>
+        <v>-0.4074</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.0662</v>
+        <v>-8.314399999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.9831</v>
+        <v>-3.4279</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.0831</v>
+        <v>-4.8865</v>
       </c>
       <c r="G14" t="n">
         <v>-6.6993</v>
@@ -1546,13 +1546,13 @@
         <v>1.9822</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8071</v>
+        <v>-1.0553</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.7471</v>
+        <v>-1.1919</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0599</v>
+        <v>0.1366</v>
       </c>
       <c r="V14" t="n">
         <v>-2.3438</v>
@@ -1579,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-13.1417</v>
+        <v>-11.8937</v>
       </c>
       <c r="E15" t="n">
-        <v>4.907099999999998</v>
+        <v>6.155000000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>-18.0488</v>
+        <v>-18.0487</v>
       </c>
       <c r="G15" t="n">
         <v>-20.4953</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3299000000000003</v>
+        <v>0.3298999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>-20.825</v>
@@ -1624,10 +1624,10 @@
         <v>14.8667</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.0736</v>
+        <v>-0.8254999999999998</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.440300000000001</v>
+        <v>-3.1923</v>
       </c>
       <c r="U15" t="n">
         <v>2.3666</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>G. CARRAL ESCUDERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9066</v>
+        <v>6.9792</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0454</v>
+        <v>7.5808</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8613</v>
+        <v>-0.6016</v>
       </c>
       <c r="G16" t="n">
-        <v>5.8416</v>
+        <v>6.562</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3475</v>
+        <v>1.5266</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4941</v>
+        <v>5.0354</v>
       </c>
       <c r="J16" t="n">
-        <v>6.2687</v>
+        <v>8.4115</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3407</v>
+        <v>3.2688</v>
       </c>
       <c r="L16" t="n">
-        <v>0.928</v>
+        <v>5.1427</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4271</v>
+        <v>-1.8495</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9932</v>
+        <v>-1.7422</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5661</v>
+        <v>-0.1073</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.5769</v>
+        <v>0.1982</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.3698</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6351</v>
+        <v>-0.3846</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1396</v>
+        <v>-0.4432</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4954</v>
+        <v>0.0586</v>
       </c>
       <c r="V16" t="n">
-        <v>2.0068</v>
+        <v>0.6036</v>
       </c>
       <c r="W16" t="n">
-        <v>2.0068</v>
+        <v>0.6036</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. DAVID ROCHA</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.3808</v>
+        <v>6.8324</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8339</v>
+        <v>4.8416</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5469</v>
+        <v>1.9908</v>
       </c>
       <c r="G17" t="n">
-        <v>4.8279</v>
+        <v>5.8416</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2879</v>
+        <v>4.3475</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1158</v>
+        <v>1.4941</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7851</v>
+        <v>6.2687</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4464</v>
+        <v>5.3407</v>
       </c>
       <c r="L17" t="n">
-        <v>3.3386</v>
+        <v>0.928</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0428</v>
+        <v>-0.4271</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7343</v>
+        <v>-0.9932</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7771</v>
+        <v>0.5661</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5947</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1805</v>
+        <v>-3.3698</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4846</v>
+        <v>1.5609</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2997</v>
+        <v>-0.0641</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1849</v>
+        <v>1.625</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.337</v>
+        <v>2.0068</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0704</v>
+        <v>2.0068</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. CARRAL ESCUDERO</t>
+          <t>D. DAVID ROCHA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.4255</v>
+        <v>5.7058</v>
       </c>
       <c r="E18" t="n">
-        <v>7.2752</v>
+        <v>2.917</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8497</v>
+        <v>2.7888</v>
       </c>
       <c r="G18" t="n">
-        <v>6.562</v>
+        <v>4.8279</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5266</v>
+        <v>-0.2879</v>
       </c>
       <c r="I18" t="n">
-        <v>5.0354</v>
+        <v>5.1158</v>
       </c>
       <c r="J18" t="n">
-        <v>8.4115</v>
+        <v>4.7851</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2688</v>
+        <v>1.4464</v>
       </c>
       <c r="L18" t="n">
-        <v>5.1427</v>
+        <v>3.3386</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8495</v>
+        <v>0.0428</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7422</v>
+        <v>-1.7343</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1073</v>
+        <v>1.7771</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1982</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9911</v>
+        <v>-2.1805</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9383</v>
+        <v>1.8096</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7488</v>
+        <v>0.3828</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1895</v>
+        <v>1.4268</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6036</v>
+        <v>-0.337</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6036</v>
+        <v>-0.0704</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. VARGAS VIVANCO</t>
+          <t>A. MORENO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.0855</v>
+        <v>4.4345</v>
       </c>
       <c r="E19" t="n">
-        <v>6.7336</v>
+        <v>3.257</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6481</v>
+        <v>1.1775</v>
       </c>
       <c r="G19" t="n">
-        <v>3.8693</v>
+        <v>5.1386</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.621</v>
+        <v>-2.4262</v>
       </c>
       <c r="I19" t="n">
-        <v>4.4903</v>
+        <v>7.5648</v>
       </c>
       <c r="J19" t="n">
-        <v>5.6585</v>
+        <v>6.0313</v>
       </c>
       <c r="K19" t="n">
-        <v>1.191</v>
+        <v>-0.2883</v>
       </c>
       <c r="L19" t="n">
-        <v>4.4675</v>
+        <v>6.3196</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7893</v>
+        <v>-0.8927</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8121</v>
+        <v>-2.1379</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0228</v>
+        <v>1.2452</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9911</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1714</v>
+        <v>0.2275</v>
       </c>
       <c r="T19" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.2568</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2376</v>
+        <v>0.4844</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6036</v>
+        <v>-0.337</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2071</v>
+        <v>-0.337</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MORENO</t>
+          <t>C. VARGAS VIVANCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.4654</v>
+        <v>4.3486</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8495</v>
+        <v>6.6317</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6159</v>
+        <v>-2.2831</v>
       </c>
       <c r="G20" t="n">
-        <v>5.1386</v>
+        <v>3.8693</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4262</v>
+        <v>-0.621</v>
       </c>
       <c r="I20" t="n">
-        <v>7.5648</v>
+        <v>4.4903</v>
       </c>
       <c r="J20" t="n">
-        <v>6.0313</v>
+        <v>5.6585</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2883</v>
+        <v>1.191</v>
       </c>
       <c r="L20" t="n">
-        <v>6.3196</v>
+        <v>4.4675</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8927</v>
+        <v>-1.7893</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.1379</v>
+        <v>-1.8121</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2452</v>
+        <v>0.0228</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5858</v>
+        <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7415</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6643</v>
+        <v>-0.0357</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0772</v>
+        <v>0.1275</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.337</v>
+        <v>-0.6036</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.337</v>
+        <v>1.2071</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4178</v>
+        <v>0.1967</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9534</v>
+        <v>1.259</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3712</v>
+        <v>-1.0623</v>
       </c>
       <c r="G21" t="n">
         <v>2.3229</v>
@@ -2092,13 +2092,13 @@
         <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1392</v>
+        <v>0.4753</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6129</v>
+        <v>-0.3073</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4738</v>
+        <v>0.7826</v>
       </c>
       <c r="V21" t="n">
         <v>-2.0068</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9291</v>
+        <v>-0.6555</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4977</v>
+        <v>0.2939</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4267</v>
+        <v>-0.9494</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5791</v>
@@ -2170,13 +2170,13 @@
         <v>1.3876</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4819</v>
+        <v>-0.2083</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1834</v>
+        <v>-0.3871</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2985</v>
+        <v>0.1788</v>
       </c>
       <c r="V22" t="n">
         <v>0.1408</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1836</v>
+        <v>-1.3064</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1486</v>
+        <v>-2.0468</v>
       </c>
       <c r="F23" t="n">
-        <v>0.965</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>1.1007</v>
@@ -2248,13 +2248,13 @@
         <v>0.3964</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9734</v>
+        <v>0.8506</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1762</v>
+        <v>-0.0743</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1496</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4737</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7479</v>
+        <v>-1.7244</v>
       </c>
       <c r="E24" t="n">
         <v>-0.3744</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3736</v>
+        <v>-1.35</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2032</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5448</v>
+        <v>-0.5212</v>
       </c>
       <c r="T24" t="n">
         <v>-0.3744</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1704</v>
+        <v>-0.1469</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9967</v>
+        <v>-2.5167</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0818</v>
+        <v>-1.878</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9149</v>
+        <v>-0.6387</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3797</v>
@@ -2404,13 +2404,13 @@
         <v>0.1982</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6259</v>
+        <v>-0.1459</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3744</v>
+        <v>-0.1706</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2515</v>
+        <v>0.0247</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.8762</v>
+        <v>-3.6666</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.6946</v>
+        <v>-2.5928</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1816</v>
+        <v>-1.0738</v>
       </c>
       <c r="G26" t="n">
         <v>-3.3252</v>
@@ -2482,13 +2482,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.551</v>
+        <v>-0.3414</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.301</v>
+        <v>-0.1991</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.25</v>
+        <v>-0.1423</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.9709</v>
+        <v>-4.807</v>
       </c>
       <c r="E27" t="n">
         <v>-1.8405</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.1304</v>
+        <v>-2.9665</v>
       </c>
       <c r="G27" t="n">
         <v>-1.6805</v>
@@ -2560,13 +2560,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.8255</v>
+        <v>-0.6616</v>
       </c>
       <c r="T27" t="n">
         <v>-0.4368</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3888</v>
+        <v>-0.2249</v>
       </c>
       <c r="V27" t="n">
         <v>-1.4737</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>13.1416</v>
+        <v>13.8206</v>
       </c>
       <c r="E28" t="n">
-        <v>18.0488</v>
+        <v>18.0485</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.9071</v>
+        <v>-4.2279</v>
       </c>
       <c r="G28" t="n">
         <v>20.4953</v>
@@ -2626,7 +2626,7 @@
         <v>-13.3472</v>
       </c>
       <c r="O28" t="n">
-        <v>2.2368</v>
+        <v>2.236799999999999</v>
       </c>
       <c r="P28" t="n">
         <v>-5.946800000000001</v>
@@ -2635,16 +2635,16 @@
         <v>-14.8667</v>
       </c>
       <c r="R28" t="n">
-        <v>8.920000000000002</v>
+        <v>8.92</v>
       </c>
       <c r="S28" t="n">
-        <v>2.0736</v>
+        <v>2.7527</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.3667</v>
+        <v>-2.3666</v>
       </c>
       <c r="U28" t="n">
-        <v>4.4402</v>
+        <v>5.119200000000001</v>
       </c>
       <c r="V28" t="n">
         <v>-3.4806</v>
